--- a/customers/alireza.xlsx
+++ b/customers/alireza.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="34">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -115,6 +115,12 @@
   </si>
   <si>
     <t>1405/04/19</t>
+  </si>
+  <si>
+    <t>1405/07/22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">وجه </t>
   </si>
 </sst>
 </file>
@@ -550,7 +556,7 @@
       </c>
       <c r="H2" s="9">
         <f>A23</f>
-        <v>6450000</v>
+        <v>1450000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -803,18 +809,24 @@
     <row r="18" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <f t="shared" si="0"/>
-        <v>6450000</v>
+        <v>1450000</v>
       </c>
       <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="3"/>
+      <c r="C18" s="6">
+        <v>5000000</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="F18" s="4"/>
     </row>
     <row r="19" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <f t="shared" si="0"/>
-        <v>6450000</v>
+        <v>1450000</v>
       </c>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
@@ -825,7 +837,7 @@
     <row r="20" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <f t="shared" si="0"/>
-        <v>6450000</v>
+        <v>1450000</v>
       </c>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -836,7 +848,7 @@
     <row r="21" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <f t="shared" si="0"/>
-        <v>6450000</v>
+        <v>1450000</v>
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -852,7 +864,7 @@
       </c>
       <c r="C22" s="7">
         <f>SUM(C3:C21)</f>
-        <v>7772000</v>
+        <v>12772000</v>
       </c>
       <c r="D22" s="7"/>
       <c r="E22" s="5"/>
@@ -861,7 +873,7 @@
     <row r="23" spans="1:6" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="11">
         <f>A21</f>
-        <v>6450000</v>
+        <v>1450000</v>
       </c>
       <c r="B23" s="11"/>
       <c r="C23" s="10" t="s">
